--- a/NBFC-MF/Borrowers/Th_Memcha_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Th_Memcha_Weekly.xlsx
@@ -749,31 +749,33 @@
       <c r="K1" s="7"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="22" t="str">
+      <c r="A2" s="2">
+        <v>46206</v>
+      </c>
+      <c r="B2" s="22">
         <f>IF(A2&lt;&gt;"",1,"")</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="C2" s="3"/>
-      <c r="D2" s="1" t="str">
+      <c r="D2" s="1">
         <f t="shared" ref="D2:D18" si="0">IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$9,"")</f>
-        <v/>
-      </c>
-      <c r="E2" s="1" t="str">
+        <v>700</v>
+      </c>
+      <c r="E2" s="1">
         <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$7*$K$8,"")</f>
-        <v/>
-      </c>
-      <c r="F2" s="1" t="str">
+        <v>200.51562079446532</v>
+      </c>
+      <c r="F2" s="1">
         <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),D2-E2,"")</f>
-        <v/>
-      </c>
-      <c r="G2" s="1" t="str">
+        <v>499.48437920553465</v>
+      </c>
+      <c r="G2" s="1">
         <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$7-F2,"")</f>
-        <v/>
-      </c>
-      <c r="H2" s="1" t="str">
+        <v>9500.5156207944656</v>
+      </c>
+      <c r="H2" s="1">
         <f>IF(AND($A2&lt;&gt;"",$B2&lt;&gt;""),$K$7-G2,"")</f>
-        <v/>
+        <v>499.48437920553442</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>17</v>
@@ -1116,7 +1118,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1151,7 +1153,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>11900</v>
+        <v>11200</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1186,7 +1188,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>11900</v>
+        <v>9500.5156207944656</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1221,7 +1223,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>0</v>
+        <v>499.48437920553442</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -1254,9 +1256,9 @@
       <c r="J16" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="K16" s="16" t="str">
+      <c r="K16" s="16">
         <f>IF(A2,A2, "")</f>
-        <v/>
+        <v>46206</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
@@ -1289,9 +1291,9 @@
       <c r="J17" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="K17" s="18" t="str">
+      <c r="K17" s="18">
         <f xml:space="preserve"> IF(A2,(K16 + (17*7)),"")</f>
-        <v/>
+        <v>46325</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Th_Memcha_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Th_Memcha_Weekly.xlsx
@@ -791,31 +791,33 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="19"/>
-      <c r="B3" s="23" t="str">
+      <c r="A3" s="19">
+        <v>46213</v>
+      </c>
+      <c r="B3" s="23">
         <f>IF(A3&lt;&gt;"",B2+1,"")</f>
-        <v/>
+        <v>2</v>
       </c>
       <c r="C3" s="20"/>
-      <c r="D3" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E3" s="21" t="str">
+      <c r="D3" s="21">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E3" s="21">
         <f t="shared" ref="E3:E18" si="1">IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),G2*$K$8,"")</f>
-        <v/>
-      </c>
-      <c r="F3" s="21" t="str">
+        <v>190.50017875711171</v>
+      </c>
+      <c r="F3" s="21">
         <f>IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),D3-E3,"")</f>
-        <v/>
-      </c>
-      <c r="G3" s="21" t="str">
+        <v>509.49982124288829</v>
+      </c>
+      <c r="G3" s="21">
         <f>IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),G2-F3,"")</f>
-        <v/>
-      </c>
-      <c r="H3" s="21" t="str">
+        <v>8991.0157995515765</v>
+      </c>
+      <c r="H3" s="21">
         <f t="shared" ref="H3:H18" si="2">IF(AND($A3&lt;&gt;"",$B3&lt;&gt;""),$K$7-G3,"")</f>
-        <v/>
+        <v>1008.9842004484235</v>
       </c>
       <c r="J3" s="4" t="s">
         <v>10</v>
@@ -1118,7 +1120,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1153,7 +1155,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>11200</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1188,7 +1190,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>9500.5156207944656</v>
+        <v>8991.0157995515765</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1223,7 +1225,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>499.48437920553442</v>
+        <v>1008.9842004484235</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Th_Memcha_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Th_Memcha_Weekly.xlsx
@@ -827,31 +827,33 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="22" t="str">
+      <c r="A4" s="2">
+        <v>46220</v>
+      </c>
+      <c r="B4" s="22">
         <f t="shared" ref="B4:B18" si="3">IF(A4&lt;&gt;"",B3+1,"")</f>
-        <v/>
+        <v>3</v>
       </c>
       <c r="C4" s="3"/>
-      <c r="D4" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E4" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F4" s="1" t="str">
+      <c r="D4" s="1">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E4" s="1">
+        <f t="shared" si="1"/>
+        <v>180.28391146199303</v>
+      </c>
+      <c r="F4" s="1">
         <f t="shared" ref="F4:F18" si="4">IF(AND($A4&lt;&gt;"",$B4&lt;&gt;""),D4-E4,"")</f>
-        <v/>
-      </c>
-      <c r="G4" s="1" t="str">
+        <v>519.71608853800694</v>
+      </c>
+      <c r="G4" s="1">
         <f t="shared" ref="G4:G18" si="5">IF(AND($A4&lt;&gt;"",$B4&lt;&gt;""),G3-F4,"")</f>
-        <v/>
-      </c>
-      <c r="H4" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>8471.2997110135693</v>
+      </c>
+      <c r="H4" s="1">
+        <f t="shared" si="2"/>
+        <v>1528.7002889864307</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>11</v>
@@ -1120,7 +1122,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1155,7 +1157,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>10500</v>
+        <v>9800</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1190,7 +1192,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>8991.0157995515765</v>
+        <v>8471.2997110135693</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1225,7 +1227,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>1008.9842004484235</v>
+        <v>1528.7002889864307</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Th_Memcha_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Th_Memcha_Weekly.xlsx
@@ -861,31 +861,33 @@
       <c r="K4" s="26"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="19"/>
-      <c r="B5" s="23" t="str">
+      <c r="A5" s="19">
+        <v>46228</v>
+      </c>
+      <c r="B5" s="23">
         <f t="shared" si="3"/>
-        <v/>
+        <v>4</v>
       </c>
       <c r="C5" s="20"/>
-      <c r="D5" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E5" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F5" s="21" t="str">
+      <c r="D5" s="21">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E5" s="21">
+        <f t="shared" si="1"/>
+        <v>169.86279204898605</v>
+      </c>
+      <c r="F5" s="21">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G5" s="21" t="str">
+        <v>530.13720795101392</v>
+      </c>
+      <c r="G5" s="21">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H5" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>7941.1625030625555</v>
+      </c>
+      <c r="H5" s="21">
+        <f t="shared" si="2"/>
+        <v>2058.8374969374445</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>12</v>
@@ -893,31 +895,33 @@
       <c r="K5" s="26"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="22" t="str">
+      <c r="A6" s="2">
+        <v>46234</v>
+      </c>
+      <c r="B6" s="22">
         <f t="shared" si="3"/>
-        <v/>
+        <v>5</v>
       </c>
       <c r="C6" s="3"/>
-      <c r="D6" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E6" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F6" s="1" t="str">
+      <c r="D6" s="1">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E6" s="1">
+        <f t="shared" si="1"/>
+        <v>159.23271291313185</v>
+      </c>
+      <c r="F6" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G6" s="1" t="str">
+        <v>540.76728708686812</v>
+      </c>
+      <c r="G6" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H6" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>7400.3952159756873</v>
+      </c>
+      <c r="H6" s="1">
+        <f t="shared" si="2"/>
+        <v>2599.6047840243127</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>13</v>
@@ -925,31 +929,33 @@
       <c r="K6" s="26"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="19"/>
-      <c r="B7" s="23" t="str">
+      <c r="A7" s="19">
+        <v>46241</v>
+      </c>
+      <c r="B7" s="23">
         <f t="shared" si="3"/>
-        <v/>
+        <v>6</v>
       </c>
       <c r="C7" s="20"/>
-      <c r="D7" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E7" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F7" s="21" t="str">
+      <c r="D7" s="21">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E7" s="21">
+        <f t="shared" si="1"/>
+        <v>148.38948408557562</v>
+      </c>
+      <c r="F7" s="21">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G7" s="21" t="str">
+        <v>551.61051591442435</v>
+      </c>
+      <c r="G7" s="21">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H7" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>6848.7847000612628</v>
+      </c>
+      <c r="H7" s="21">
+        <f t="shared" si="2"/>
+        <v>3151.2152999387372</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>6</v>
@@ -1122,7 +1128,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1157,7 +1163,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>9800</v>
+        <v>7700</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1192,7 +1198,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>8471.2997110135693</v>
+        <v>6848.7847000612628</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1227,7 +1233,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>1528.7002889864307</v>
+        <v>3151.2152999387372</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Th_Memcha_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Th_Memcha_Weekly.xlsx
@@ -965,31 +965,33 @@
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="22" t="str">
+      <c r="A8" s="2">
+        <v>46248</v>
+      </c>
+      <c r="B8" s="22">
         <f t="shared" si="3"/>
-        <v/>
+        <v>7</v>
       </c>
       <c r="C8" s="3"/>
-      <c r="D8" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E8" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F8" s="1" t="str">
+      <c r="D8" s="1">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E8" s="1">
+        <f t="shared" si="1"/>
+        <v>137.328831582042</v>
+      </c>
+      <c r="F8" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G8" s="1" t="str">
+        <v>562.67116841795803</v>
+      </c>
+      <c r="G8" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H8" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>6286.1135316433047</v>
+      </c>
+      <c r="H8" s="1">
+        <f t="shared" si="2"/>
+        <v>3713.8864683566953</v>
       </c>
       <c r="J8" s="4" t="s">
         <v>14</v>
@@ -1128,7 +1130,7 @@
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1163,7 +1165,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>7700</v>
+        <v>7000</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1198,7 +1200,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>6848.7847000612628</v>
+        <v>6286.1135316433047</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1233,7 +1235,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>3151.2152999387372</v>
+        <v>3713.8864683566953</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">

--- a/NBFC-MF/Borrowers/Th_Memcha_Weekly.xlsx
+++ b/NBFC-MF/Borrowers/Th_Memcha_Weekly.xlsx
@@ -1002,31 +1002,33 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="19"/>
-      <c r="B9" s="23" t="str">
+      <c r="A9" s="19">
+        <v>46258</v>
+      </c>
+      <c r="B9" s="23">
         <f t="shared" si="3"/>
-        <v/>
+        <v>8</v>
       </c>
       <c r="C9" s="20"/>
-      <c r="D9" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E9" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F9" s="21" t="str">
+      <c r="D9" s="21">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E9" s="21">
+        <f t="shared" si="1"/>
+        <v>126.0463957181946</v>
+      </c>
+      <c r="F9" s="21">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G9" s="21" t="str">
+        <v>573.95360428180538</v>
+      </c>
+      <c r="G9" s="21">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H9" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>5712.1599273614993</v>
+      </c>
+      <c r="H9" s="21">
+        <f t="shared" si="2"/>
+        <v>4287.8400726385007</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>7</v>
@@ -1036,31 +1038,33 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="22" t="str">
+      <c r="A10" s="2">
+        <v>46262</v>
+      </c>
+      <c r="B10" s="22">
         <f t="shared" si="3"/>
-        <v/>
+        <v>9</v>
       </c>
       <c r="C10" s="3"/>
-      <c r="D10" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E10" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F10" s="1" t="str">
+      <c r="D10" s="1">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E10" s="1">
+        <f t="shared" si="1"/>
+        <v>114.53772939121589</v>
+      </c>
+      <c r="F10" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G10" s="1" t="str">
+        <v>585.46227060878414</v>
+      </c>
+      <c r="G10" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H10" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>5126.6976567527154</v>
+      </c>
+      <c r="H10" s="1">
+        <f t="shared" si="2"/>
+        <v>4873.3023432472846</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>8</v>
@@ -1070,67 +1074,71 @@
       </c>
     </row>
     <row r="11" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="19"/>
-      <c r="B11" s="23" t="str">
+      <c r="A11" s="19">
+        <v>46269</v>
+      </c>
+      <c r="B11" s="23">
         <f t="shared" si="3"/>
-        <v/>
+        <v>10</v>
       </c>
       <c r="C11" s="20"/>
-      <c r="D11" s="21" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E11" s="21" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F11" s="21" t="str">
+      <c r="D11" s="21">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E11" s="21">
+        <f t="shared" si="1"/>
+        <v>102.79829632693014</v>
+      </c>
+      <c r="F11" s="21">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G11" s="21" t="str">
+        <v>597.20170367306991</v>
+      </c>
+      <c r="G11" s="21">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H11" s="21" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>4529.4959530796459</v>
+      </c>
+      <c r="H11" s="21">
+        <f t="shared" si="2"/>
+        <v>5470.5040469203541</v>
       </c>
       <c r="J11" s="14"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="22" t="str">
+      <c r="A12" s="2">
+        <v>46276</v>
+      </c>
+      <c r="B12" s="22">
         <f t="shared" si="3"/>
-        <v/>
+        <v>11</v>
       </c>
       <c r="C12" s="3"/>
-      <c r="D12" s="1" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="E12" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="F12" s="1" t="str">
+      <c r="D12" s="1">
+        <f t="shared" si="0"/>
+        <v>700</v>
+      </c>
+      <c r="E12" s="1">
+        <f t="shared" si="1"/>
+        <v>90.823469291778352</v>
+      </c>
+      <c r="F12" s="1">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="G12" s="1" t="str">
+        <v>609.17653070822166</v>
+      </c>
+      <c r="G12" s="1">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="H12" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>3920.3194223714245</v>
+      </c>
+      <c r="H12" s="1">
+        <f t="shared" si="2"/>
+        <v>6079.6805776285755</v>
       </c>
       <c r="J12" s="8" t="s">
         <v>16</v>
       </c>
       <c r="K12" s="9">
         <f>IFERROR(MAX($B:$B),"")</f>
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -1165,7 +1173,7 @@
       </c>
       <c r="K13" s="11">
         <f>(K10*K9)-K9*K12</f>
-        <v>7000</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -1200,7 +1208,7 @@
       </c>
       <c r="K14" s="11">
         <f>IF(A2="", K9*K10, IFERROR(INDEX($G:$G, MATCH($K$12, $B:$B, 0)), 0))</f>
-        <v>6286.1135316433047</v>
+        <v>3920.3194223714245</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -1235,7 +1243,7 @@
       </c>
       <c r="K15" s="13">
         <f>IFERROR(INDEX($H:$H, MATCH($K$12, $B:$B, 0)), 0)</f>
-        <v>3713.8864683566953</v>
+        <v>6079.6805776285755</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
